--- a/Outputs/Recycling_Plot_Data/ACCII/06_Needed_Recycling_Capacity_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/06_Needed_Recycling_Capacity_data_ACCII.xlsx
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>0.05122860885037319</v>
+        <v>0.0423249556020716</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>0.2886390878274682</v>
+        <v>0.2672641577791426</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="F28">
-        <v>0.8119380732177076</v>
+        <v>0.7552867011568123</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>0.03880546583723929</v>
+        <v>0.003529023824669537</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>1.598090210099351</v>
+        <v>1.500422563090463</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>0.3404640831658824</v>
+        <v>0.2641713662053201</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>2.665451438645296</v>
+        <v>2.524944214491547</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>0.9233317921588272</v>
+        <v>0.8041994980534043</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F34">
-        <v>4.025165637900709</v>
+        <v>3.844952778987691</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="F35">
-        <v>1.79855247186124</v>
+        <v>1.639714542996548</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="F36">
-        <v>5.689993478566964</v>
+        <v>5.477174940304743</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>2.978886792974496</v>
+        <v>2.787443184760599</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>7.675722056510022</v>
+        <v>7.438690741683592</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="F39">
-        <v>4.480121851364553</v>
+        <v>4.264465466586448</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>9.99675612914911</v>
+        <v>9.742727745459167</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>6.316662404450642</v>
+        <v>6.084008950809024</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>12.6650933070228</v>
+        <v>12.39906406201851</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>8.500506062771326</v>
+        <v>8.255851747815369</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="F44">
-        <v>15.69094174956054</v>
+        <v>15.41591727327616</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>11.04186098575607</v>
+        <v>10.78821143952001</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>19.07211436112968</v>
+        <v>18.78973346491058</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>13.93854007777221</v>
+        <v>13.67753411160144</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>22.80049057920754</v>
+        <v>22.51151912275456</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="F49">
-        <v>17.18242277629707</v>
+        <v>16.91482624989242</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>26.85744387245386</v>
+        <v>26.5619916551382</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>20.75488254999039</v>
+        <v>20.48080526272307</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>31.2221623822448</v>
+        <v>30.91968313679073</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="F53">
-        <v>24.63510754022833</v>
+        <v>24.35400322482259</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="F76">
-        <v>0.05395311933398678</v>
+        <v>0.04504807226324151</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="F78">
-        <v>0.2956397368313765</v>
+        <v>0.274258949429234</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="F80">
-        <v>0.8254888390045219</v>
+        <v>0.7688274829887497</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>0.04535558262014529</v>
+        <v>0.01007501400651562</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="F82">
-        <v>1.622014697606181</v>
+        <v>1.524329431113623</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="F83">
-        <v>0.357387921668804</v>
+        <v>0.2810834425783885</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="F84">
-        <v>2.705880026401279</v>
+        <v>2.565341901566373</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>0.9567597309109015</v>
+        <v>0.837602393478139</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="F86">
-        <v>4.09099747514543</v>
+        <v>3.910732598773124</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>1.857383660102053</v>
+        <v>1.69849957113189</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>5.793105700816268</v>
+        <v>5.580205324019534</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="F89">
-        <v>3.074998366219891</v>
+        <v>2.8834787768253</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="F90">
-        <v>7.830971642445975</v>
+        <v>7.59381928798715</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F91">
-        <v>4.628370788296597</v>
+        <v>4.412599221239915</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="F92">
-        <v>10.22146568818128</v>
+        <v>9.967266132048294</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="F93">
-        <v>6.5343713144789</v>
+        <v>6.301552545748059</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="F94">
-        <v>12.97880190624052</v>
+        <v>12.71253683511041</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="F95">
-        <v>8.807214012985142</v>
+        <v>8.562329729257174</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F96">
-        <v>16.11548829382242</v>
+        <v>15.84014247165286</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="F97">
-        <v>11.45940688101405</v>
+        <v>11.20544184624662</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="F98">
-        <v>19.63116121506528</v>
+        <v>19.34834222868015</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="F99">
-        <v>14.4905862827039</v>
+        <v>14.22914808372091</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="F100">
-        <v>23.51916516638448</v>
+        <v>23.22959379772638</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F101">
-        <v>17.8940967144701</v>
+        <v>17.62590613321414</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="F102">
-        <v>27.76129191650593</v>
+        <v>27.46501564679914</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="F103">
-        <v>21.65172994503855</v>
+        <v>21.3768344627339</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="F104">
-        <v>32.33640918089113</v>
+        <v>32.03279366922528</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="F105">
-        <v>25.74235368987076</v>
+        <v>25.46011896560704</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="F126">
-        <v>0.07053070376669167</v>
+        <v>0.06431553807179216</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="F128">
-        <v>0.3291540969040772</v>
+        <v>0.3139053326723356</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="F130">
-        <v>0.8151179839311582</v>
+        <v>0.7871690293046393</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="F131">
-        <v>0.001470367474080878</v>
+        <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F132">
-        <v>1.645392685261847</v>
+        <v>1.581295047151852</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="F133">
-        <v>0.3472515492517693</v>
+        <v>0.3096324982942129</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="F134">
-        <v>2.818888223775386</v>
+        <v>2.712705767881547</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="F135">
-        <v>1.036253568212309</v>
+        <v>0.9565496994709077</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="F136">
-        <v>4.381071334672668</v>
+        <v>4.230850650041941</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="F137">
-        <v>2.113943159556591</v>
+        <v>1.990201062078302</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="F138">
-        <v>6.375564670670887</v>
+        <v>6.184412756090248</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="F139">
-        <v>3.623942976001809</v>
+        <v>3.459269648573609</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="F140">
-        <v>8.849492217019293</v>
+        <v>8.624567591593459</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="F141">
-        <v>5.613377002797216</v>
+        <v>5.414930964523821</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="F142">
-        <v>11.85591479377842</v>
+        <v>11.60570118526589</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="F143">
-        <v>8.135306060003337</v>
+        <v>7.911571038643248</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="F144">
-        <v>15.44529436242091</v>
+        <v>15.1770588502057</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="F145">
-        <v>11.24019210909283</v>
+        <v>10.99843518403006</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="F146">
-        <v>19.66480526000947</v>
+        <v>19.3835010910041</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="F147">
-        <v>14.97520948712839</v>
+        <v>14.72038390527546</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="F148">
-        <v>24.56036257216517</v>
+        <v>24.26883195446919</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="F149">
-        <v>19.3862732797311</v>
+        <v>19.12122124918755</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="F150">
-        <v>30.15924463135625</v>
+        <v>29.85880691337917</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="F151">
-        <v>24.50066181936917</v>
+        <v>24.22670268854453</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="F152">
-        <v>36.47749910901189</v>
+        <v>36.16841586864322</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="F153">
-        <v>30.33442277747181</v>
+        <v>30.05181812425559</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="F154">
-        <v>43.49484642986718</v>
+        <v>43.1765164396454</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="F155">
-        <v>36.8672765787741</v>
+        <v>36.57542517570476</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="F156">
-        <v>51.17814752072332</v>
+        <v>50.84900090784708</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="F157">
-        <v>44.06608415007724</v>
+        <v>43.76341612435344</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="F178">
-        <v>0.07282292602617638</v>
+        <v>0.066606921035718</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="F180">
-        <v>0.3351731086089635</v>
+        <v>0.319920586330634</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="F182">
-        <v>0.8270527357844601</v>
+        <v>0.7990916795373851</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="F183">
-        <v>0.007386107622496435</v>
+        <v>0</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="F184">
-        <v>1.666488432628985</v>
+        <v>1.602369195025463</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="F185">
-        <v>0.3623282849140217</v>
+        <v>0.3187839959350778</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="F186">
-        <v>2.854490994788677</v>
+        <v>2.748271268401658</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="F187">
-        <v>1.065837327520713</v>
+        <v>0.980192549758273</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="F188">
-        <v>4.439723933802867</v>
+        <v>4.289440983360755</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="F189">
-        <v>2.166576746981903</v>
+        <v>2.03686874516437</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="F190">
-        <v>6.469882266837244</v>
+        <v>6.278630557550217</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="F191">
-        <v>3.712241560463279</v>
+        <v>3.541564799800831</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="F192">
-        <v>8.996804691386066</v>
+        <v>8.771728979937782</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="F193">
-        <v>5.754670465459101</v>
+        <v>5.550169702635397</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="F194">
-        <v>12.07871392209932</v>
+        <v>11.82828309176393</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="F195">
-        <v>8.352086176619357</v>
+        <v>8.122230294908546</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="F196">
-        <v>15.77098449257159</v>
+        <v>15.50244800979677</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="F197">
-        <v>11.55986322753863</v>
+        <v>11.31190169338838</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="F198">
-        <v>20.12577148169528</v>
+        <v>19.84405832737426</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="F199">
-        <v>15.43015669710932</v>
+        <v>15.16901849141288</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="F200">
-        <v>25.19449252515214</v>
+        <v>24.90240900676796</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="F201">
-        <v>20.01438422101317</v>
+        <v>19.74287565125358</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="F202">
-        <v>31.00946449904202</v>
+        <v>30.70827506579807</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="F203">
-        <v>25.34486267535006</v>
+        <v>25.06424819073069</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="F204">
-        <v>37.59134122584158</v>
+        <v>37.28122700075373</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="F205">
-        <v>31.44224588259661</v>
+        <v>31.15270660613335</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="F206">
-        <v>44.9217771338536</v>
+        <v>44.60202525409468</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="F207">
-        <v>38.28818827105562</v>
+        <v>37.9890113399213</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="F208">
-        <v>52.96786748811714</v>
+        <v>52.63674950777474</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="F209">
-        <v>45.84978510576617</v>
+        <v>45.53924207404835</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
